--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FA7184-BEB1-480E-A943-BBC733B80281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE1653C-AA56-45EC-A325-2568C5E10110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,177 +36,241 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t>TWONTO</t>
   </si>
   <si>
-    <t>SWG_x000D_
-CB_x000D_
-LB_x000D_
-TB_x000D_
-LVS</t>
-  </si>
-  <si>
-    <t>PDSH_x000D_
-PDSHH_x000D_
-PSH_x000D_
-PSHH_x000D_
-PSL_x000D_
-PSLL</t>
-  </si>
-  <si>
-    <t>PDIT_x000D_
-PDT</t>
-  </si>
-  <si>
-    <t>ANL_x000D_
-METR_x000D_
-SW</t>
-  </si>
-  <si>
-    <t>ZSH_x000D_
-ZSLH_x000D_
-ZSL</t>
-  </si>
-  <si>
     <t>SIT</t>
   </si>
   <si>
-    <t>TSH_x000D_
-TSL</t>
-  </si>
-  <si>
-    <t>LSH_x000D_
-LSHH_x000D_
-LSL_x000D_
-LSLL_x000D_
-LSM</t>
-  </si>
-  <si>
     <t>LDIT</t>
   </si>
   <si>
     <t>DPU</t>
   </si>
   <si>
-    <t>FSH_x000D_
-FSL</t>
-  </si>
-  <si>
-    <t>SSH_x000D_
-SSL</t>
-  </si>
-  <si>
-    <t>EIT_x000D_
-IRT_x000D_
-IIT_x000D_
-JRT_x000D_
-JIT</t>
-  </si>
-  <si>
-    <t>FI_x000D_
-LI_x000D_
-PI_x000D_
-SI_x000D_
-TI</t>
-  </si>
-  <si>
-    <t>VSH_x000D_
-VSL</t>
-  </si>
-  <si>
     <t>CYC</t>
   </si>
   <si>
-    <t>WSH_x000D_
-WSL</t>
-  </si>
-  <si>
     <t>SL</t>
   </si>
   <si>
-    <t>MCC</t>
-  </si>
-  <si>
-    <t>PD_x000D_
-SD</t>
-  </si>
-  <si>
     <t>LTX</t>
   </si>
   <si>
     <t>Super_Tag</t>
   </si>
   <si>
-    <t>breaker</t>
-  </si>
-  <si>
-    <t>pressure_switch</t>
-  </si>
-  <si>
-    <t>pressure_transmitter</t>
-  </si>
-  <si>
-    <t>instrumentation</t>
-  </si>
-  <si>
-    <t>position_switch</t>
-  </si>
-  <si>
-    <t>instrument_transmitter</t>
-  </si>
-  <si>
-    <t>temperature_switch</t>
-  </si>
-  <si>
-    <t>level_switch</t>
-  </si>
-  <si>
-    <t>level_transmitter</t>
-  </si>
-  <si>
-    <t>polymer_preparation_system</t>
-  </si>
-  <si>
-    <t>flow_switch</t>
-  </si>
-  <si>
-    <t>speed_switch</t>
-  </si>
-  <si>
-    <t>electrical_current_sensing_instrument</t>
-  </si>
-  <si>
-    <t>instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>vibration_sensor_element</t>
-  </si>
-  <si>
-    <t>classifier</t>
-  </si>
-  <si>
-    <t>weight_switch</t>
-  </si>
-  <si>
-    <t>air_duct_segment</t>
-  </si>
-  <si>
-    <t>electrical_panel_or_cabinet</t>
-  </si>
-  <si>
-    <t>digester_tank</t>
-  </si>
-  <si>
-    <t>lighting_unit</t>
+    <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
+PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
+PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
+PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
+PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
+SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
+WHERE { 
+    ?entityIRI tw:is_superclass_of_tag_code ?object ;
+              rdfs:label ?label .
+}</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>LSH</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>EIT</t>
+  </si>
+  <si>
+    <t>LSM</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>LSHH</t>
+  </si>
+  <si>
+    <t>VSH</t>
+  </si>
+  <si>
+    <t>LVS</t>
+  </si>
+  <si>
+    <t>PDIT</t>
+  </si>
+  <si>
+    <t>ZSH</t>
+  </si>
+  <si>
+    <t>ZSL</t>
+  </si>
+  <si>
+    <t>PDSHH</t>
+  </si>
+  <si>
+    <t>VSL</t>
+  </si>
+  <si>
+    <t>PDSH</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>JRT</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>ZSLH</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>JIT</t>
+  </si>
+  <si>
+    <t>PSHH</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>WSL</t>
+  </si>
+  <si>
+    <t>SSL</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>LSLL</t>
+  </si>
+  <si>
+    <t>IRT</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>IIT</t>
+  </si>
+  <si>
+    <t>FSH</t>
+  </si>
+  <si>
+    <t>FSL</t>
+  </si>
+  <si>
+    <t>SWG</t>
+  </si>
+  <si>
+    <t>TSH</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>PDT</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>PSLL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#polymer_preparation_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#breaker</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vibration_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
+  </si>
+  <si>
+    <t>MSL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#digester_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,15 +286,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -241,12 +298,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -262,14 +313,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -315,8 +362,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B23" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B23" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B52" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B52" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -622,218 +669,425 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A2:B118"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="3"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" s="3"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B46" s="3"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B57" s="3"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B62" s="3"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B67" s="3"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B76" s="3"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B87" s="3"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B106" s="3"/>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B118" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE1653C-AA56-45EC-A325-2568C5E10110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8510780-6757-45BF-AA64-C84D6F2126ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>TWONTO</t>
   </si>
@@ -77,99 +77,30 @@
     <t>LI</t>
   </si>
   <si>
-    <t>LSH</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>EIT</t>
-  </si>
-  <si>
-    <t>LSM</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>LSHH</t>
-  </si>
-  <si>
-    <t>VSH</t>
-  </si>
-  <si>
     <t>LVS</t>
   </si>
   <si>
     <t>PDIT</t>
   </si>
   <si>
-    <t>ZSH</t>
-  </si>
-  <si>
-    <t>ZSL</t>
-  </si>
-  <si>
-    <t>PDSHH</t>
-  </si>
-  <si>
-    <t>VSL</t>
-  </si>
-  <si>
-    <t>PDSH</t>
-  </si>
-  <si>
     <t>LB</t>
   </si>
   <si>
-    <t>JRT</t>
-  </si>
-  <si>
     <t>TB</t>
   </si>
   <si>
     <t>CB</t>
   </si>
   <si>
-    <t>ZSLH</t>
-  </si>
-  <si>
     <t>FI</t>
   </si>
   <si>
-    <t>JIT</t>
-  </si>
-  <si>
-    <t>PSHH</t>
-  </si>
-  <si>
     <t>PD</t>
   </si>
   <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>WSL</t>
-  </si>
-  <si>
-    <t>SSL</t>
-  </si>
-  <si>
-    <t>SSH</t>
-  </si>
-  <si>
-    <t>LSLL</t>
-  </si>
-  <si>
-    <t>IRT</t>
-  </si>
-  <si>
     <t>PI</t>
   </si>
   <si>
-    <t>IIT</t>
-  </si>
-  <si>
     <t>FSH</t>
   </si>
   <si>
@@ -179,48 +110,24 @@
     <t>SWG</t>
   </si>
   <si>
-    <t>TSH</t>
-  </si>
-  <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>TSL</t>
-  </si>
-  <si>
     <t>SD</t>
   </si>
   <si>
-    <t>PSH</t>
-  </si>
-  <si>
     <t>PDT</t>
   </si>
   <si>
     <t>SI</t>
   </si>
   <si>
-    <t>PSLL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
   </si>
   <si>
@@ -230,27 +137,9 @@
     <t>http://www.toronto.ca/TWONTO#breaker</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
-    <t>MSL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#digester_tank</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#position_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#flow_switch</t>
   </si>
   <si>
@@ -261,9 +150,6 @@
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
   </si>
 </sst>
 </file>
@@ -362,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B52" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B52" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B23" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B23" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -373,9 +259,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -413,7 +299,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -519,7 +405,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -661,7 +547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -669,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -691,402 +577,170 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8510780-6757-45BF-AA64-C84D6F2126ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9361B62F-8A10-449F-AB77-1C7FCEABA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>TWONTO</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>CYC</t>
-  </si>
-  <si>
-    <t>SL</t>
   </si>
   <si>
     <t>LTX</t>
@@ -146,10 +143,49 @@
     <t>http://www.toronto.ca/TWONTO#classifier</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
+  </si>
+  <si>
+    <t>IRT</t>
+  </si>
+  <si>
+    <t>JIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
+  </si>
+  <si>
+    <t>MSL</t>
+  </si>
+  <si>
+    <t>JRT</t>
+  </si>
+  <si>
+    <t>EIT</t>
+  </si>
+  <si>
+    <t>SSL</t>
+  </si>
+  <si>
+    <t>IIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
+  </si>
+  <si>
+    <t>WSL</t>
+  </si>
+  <si>
+    <t>WSH</t>
   </si>
 </sst>
 </file>
@@ -248,8 +284,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B23" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B23" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B32" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B32" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -555,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -564,7 +600,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,103 +608,103 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,71 +712,143 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9361B62F-8A10-449F-AB77-1C7FCEABA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95631B3-6A33-40FE-9E61-B287C4459F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
   <si>
     <t>TWONTO</t>
   </si>
@@ -186,6 +186,30 @@
   </si>
   <si>
     <t>WSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>BUS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#600V_receptacle</t>
+  </si>
+  <si>
+    <t>WR</t>
+  </si>
+  <si>
+    <t>PDP</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>PR</t>
   </si>
 </sst>
 </file>
@@ -284,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B32" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B32" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B38" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B38" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -591,19 +615,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -619,7 +643,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -627,7 +651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -635,7 +659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -643,7 +667,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -651,7 +675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -659,7 +683,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -667,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -675,7 +699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -683,7 +707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -691,7 +715,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -699,7 +723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -707,148 +731,196 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B37" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95631B3-6A33-40FE-9E61-B287C4459F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8377FC-CECB-49DE-9681-2C0B91C39F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,157 +59,157 @@
     <t>Super_Tag</t>
   </si>
   <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>LVS</t>
+  </si>
+  <si>
+    <t>PDIT</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>FSH</t>
+  </si>
+  <si>
+    <t>FSL</t>
+  </si>
+  <si>
+    <t>SWG</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>PDT</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#polymer_preparation_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#breaker</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#digester_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
+  </si>
+  <si>
+    <t>IRT</t>
+  </si>
+  <si>
+    <t>JIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
+  </si>
+  <si>
+    <t>MSL</t>
+  </si>
+  <si>
+    <t>JRT</t>
+  </si>
+  <si>
+    <t>EIT</t>
+  </si>
+  <si>
+    <t>SSL</t>
+  </si>
+  <si>
+    <t>IIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
+  </si>
+  <si>
+    <t>WSL</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>BUS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#600V_receptacle</t>
+  </si>
+  <si>
+    <t>WR</t>
+  </si>
+  <si>
+    <t>PDP</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
 PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
+SELECT ?TWONTO (STR(?object) as ?Avantis)
 WHERE { 
-    ?entityIRI tw:is_superclass_of_tag_code ?object ;
-              rdfs:label ?label .
+    ?TWONTO tw:is_superclass_of_tag_code ?object .
+    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>LVS</t>
-  </si>
-  <si>
-    <t>PDIT</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>CB</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>PD</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>FSH</t>
-  </si>
-  <si>
-    <t>FSL</t>
-  </si>
-  <si>
-    <t>SWG</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>PDT</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#polymer_preparation_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#breaker</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#digester_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
-  </si>
-  <si>
-    <t>SSH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
-  </si>
-  <si>
-    <t>IRT</t>
-  </si>
-  <si>
-    <t>JIT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
-    <t>MSL</t>
-  </si>
-  <si>
-    <t>JRT</t>
-  </si>
-  <si>
-    <t>EIT</t>
-  </si>
-  <si>
-    <t>SSL</t>
-  </si>
-  <si>
-    <t>IIT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
-  </si>
-  <si>
-    <t>WSL</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
-  </si>
-  <si>
-    <t>BUS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#600V_receptacle</t>
-  </si>
-  <si>
-    <t>WR</t>
-  </si>
-  <si>
-    <t>PDP</t>
-  </si>
-  <si>
-    <t>MCC</t>
-  </si>
-  <si>
-    <t>PR</t>
   </si>
 </sst>
 </file>
@@ -622,9 +622,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -637,39 +637,39 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -677,15 +677,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -701,119 +701,119 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
@@ -821,63 +821,63 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -885,42 +885,42 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
         <v>44</v>
-      </c>
-      <c r="B35" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8377FC-CECB-49DE-9681-2C0B91C39F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B508CDE-50E2-491F-9B1B-FFC63AA7B592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="81">
   <si>
     <t>TWONTO</t>
   </si>
@@ -210,6 +210,84 @@
     ?TWONTO tw:is_superclass_of_tag_code ?object .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_switch</t>
+  </si>
+  <si>
+    <t>LSM</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_switch</t>
+  </si>
+  <si>
+    <t>ZSLH</t>
+  </si>
+  <si>
+    <t>LSH</t>
+  </si>
+  <si>
+    <t>LSHH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>ZSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
+  </si>
+  <si>
+    <t>PSLL</t>
+  </si>
+  <si>
+    <t>ZSL</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vibration_sensor_element</t>
+  </si>
+  <si>
+    <t>VSH</t>
+  </si>
+  <si>
+    <t>VSL</t>
+  </si>
+  <si>
+    <t>LSLL</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>PDSH</t>
+  </si>
+  <si>
+    <t>PDSHH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
+  </si>
+  <si>
+    <t>TSH</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>PSHH</t>
   </si>
 </sst>
 </file>
@@ -308,8 +386,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B38" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B38" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B58" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B58" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -615,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -637,138 +715,138 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -781,50 +859,50 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -832,31 +910,31 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -864,63 +942,223 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B508CDE-50E2-491F-9B1B-FFC63AA7B592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CBCE23-193B-474E-B960-16B111038684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,54 +104,15 @@
     <t>SI</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#polymer_preparation_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#breaker</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#digester_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_current_sensing_instrument</t>
-  </si>
-  <si>
     <t>IRT</t>
   </si>
   <si>
     <t>JIT</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
     <t>MSL</t>
   </si>
   <si>
@@ -167,27 +128,15 @@
     <t>IIT</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#weight_switch</t>
-  </si>
-  <si>
     <t>WSL</t>
   </si>
   <si>
     <t>WSH</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
-  </si>
-  <si>
     <t>BUS</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#600V_receptacle</t>
-  </si>
-  <si>
     <t>WR</t>
   </si>
   <si>
@@ -198,6 +147,135 @@
   </si>
   <si>
     <t>PR</t>
+  </si>
+  <si>
+    <t>LSM</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>ZSLH</t>
+  </si>
+  <si>
+    <t>LSH</t>
+  </si>
+  <si>
+    <t>LSHH</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>ZSH</t>
+  </si>
+  <si>
+    <t>PSLL</t>
+  </si>
+  <si>
+    <t>ZSL</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>VSH</t>
+  </si>
+  <si>
+    <t>VSL</t>
+  </si>
+  <si>
+    <t>LSLL</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>PDSH</t>
+  </si>
+  <si>
+    <t>PDSHH</t>
+  </si>
+  <si>
+    <t>TSH</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>PSHH</t>
+  </si>
+  <si>
+    <t>600V receptacle</t>
+  </si>
+  <si>
+    <t>electrical current sensing instrument</t>
+  </si>
+  <si>
+    <t>breaker</t>
+  </si>
+  <si>
+    <t>weight switch</t>
+  </si>
+  <si>
+    <t>digester tank</t>
+  </si>
+  <si>
+    <t>pressure switch</t>
+  </si>
+  <si>
+    <t>lighting unit</t>
+  </si>
+  <si>
+    <t>pressure transmitter</t>
+  </si>
+  <si>
+    <t>flow switch</t>
+  </si>
+  <si>
+    <t>polymer preparation system</t>
+  </si>
+  <si>
+    <t>vibration sensor element</t>
+  </si>
+  <si>
+    <t>instrument gauge or display</t>
+  </si>
+  <si>
+    <t>air duct segment</t>
+  </si>
+  <si>
+    <t>temperature switch</t>
+  </si>
+  <si>
+    <t>level switch</t>
+  </si>
+  <si>
+    <t>LV electrical panel</t>
+  </si>
+  <si>
+    <t>position switch</t>
+  </si>
+  <si>
+    <t>instrument transmitter</t>
+  </si>
+  <si>
+    <t>MV electrical cabinet</t>
+  </si>
+  <si>
+    <t>classifier</t>
+  </si>
+  <si>
+    <t>speed switch</t>
+  </si>
+  <si>
+    <t>level transmitter</t>
+  </si>
+  <si>
+    <t>motion sensor element</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -205,89 +283,12 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT ?TWONTO (STR(?object) as ?Avantis)
+SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis) 
 WHERE { 
     ?TWONTO tw:is_superclass_of_tag_code ?object .
+    ?TWONTO rdfs:label ?TWONTO_Label .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
-    <t>LSM</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_switch</t>
-  </si>
-  <si>
-    <t>ZSLH</t>
-  </si>
-  <si>
-    <t>LSH</t>
-  </si>
-  <si>
-    <t>LSHH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>ZSH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
-  </si>
-  <si>
-    <t>PSLL</t>
-  </si>
-  <si>
-    <t>ZSL</t>
-  </si>
-  <si>
-    <t>PSH</t>
-  </si>
-  <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_sensor_element</t>
-  </si>
-  <si>
-    <t>VSH</t>
-  </si>
-  <si>
-    <t>VSL</t>
-  </si>
-  <si>
-    <t>LSLL</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>PDSH</t>
-  </si>
-  <si>
-    <t>PDSHH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
-  </si>
-  <si>
-    <t>TSH</t>
-  </si>
-  <si>
-    <t>TSL</t>
-  </si>
-  <si>
-    <t>PSHH</t>
   </si>
 </sst>
 </file>
@@ -700,9 +701,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -715,399 +716,399 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
@@ -1115,50 +1116,50 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CBCE23-193B-474E-B960-16B111038684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38508669-B046-4F3F-BFB1-6FE7B63762D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -209,86 +209,85 @@
     <t>PSHH</t>
   </si>
   <si>
-    <t>600V receptacle</t>
-  </si>
-  <si>
-    <t>electrical current sensing instrument</t>
-  </si>
-  <si>
-    <t>breaker</t>
-  </si>
-  <si>
-    <t>weight switch</t>
-  </si>
-  <si>
-    <t>digester tank</t>
-  </si>
-  <si>
-    <t>pressure switch</t>
-  </si>
-  <si>
-    <t>lighting unit</t>
-  </si>
-  <si>
-    <t>pressure transmitter</t>
-  </si>
-  <si>
-    <t>flow switch</t>
-  </si>
-  <si>
-    <t>polymer preparation system</t>
-  </si>
-  <si>
-    <t>vibration sensor element</t>
-  </si>
-  <si>
-    <t>instrument gauge or display</t>
-  </si>
-  <si>
-    <t>air duct segment</t>
-  </si>
-  <si>
-    <t>temperature switch</t>
-  </si>
-  <si>
-    <t>level switch</t>
-  </si>
-  <si>
-    <t>LV electrical panel</t>
-  </si>
-  <si>
-    <t>position switch</t>
-  </si>
-  <si>
-    <t>instrument transmitter</t>
-  </si>
-  <si>
-    <t>MV electrical cabinet</t>
-  </si>
-  <si>
-    <t>classifier</t>
-  </si>
-  <si>
-    <t>speed switch</t>
-  </si>
-  <si>
-    <t>level transmitter</t>
-  </si>
-  <si>
-    <t>motion sensor element</t>
-  </si>
-  <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
 PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis) 
+SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_superclass_of_tag_code ?object .
-    ?TWONTO rdfs:label ?TWONTO_Label .
-    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
+    ?sub tw:is_superclass_of_tag_code ?object .
+    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00530</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00467</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00466</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00699</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00297</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00110</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00604</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00445</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00590</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00220</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00111</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00447</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00186</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00734</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00144</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00605</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00792</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00821</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00367</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00579</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00271</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00478</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00808</t>
   </si>
 </sst>
 </file>
@@ -701,9 +700,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -716,34 +715,34 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -751,7 +750,7 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -759,7 +758,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -767,7 +766,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -775,55 +774,55 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -831,31 +830,31 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -863,303 +862,303 @@
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supertag.xlsx
+++ b/Avantis Mapping/SPARQL_supertag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38508669-B046-4F3F-BFB1-6FE7B63762D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E22C2-B497-411D-A230-45611E7F008A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="113">
   <si>
     <t>TWONTO</t>
   </si>
@@ -288,6 +288,102 @@
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#00808</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00573</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00520</t>
+  </si>
+  <si>
+    <t>TPB</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00231</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>ANL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00489</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00298</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00477</t>
+  </si>
+  <si>
+    <t>LPU</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00920</t>
+  </si>
+  <si>
+    <t>SCAN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00919</t>
+  </si>
+  <si>
+    <t>LTG</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00756</t>
+  </si>
+  <si>
+    <t>VEH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00636</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00192</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>PRNT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00800</t>
+  </si>
+  <si>
+    <t>DVS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00526</t>
+  </si>
+  <si>
+    <t>SLFR</t>
+  </si>
+  <si>
+    <t>METR</t>
   </si>
 </sst>
 </file>
@@ -386,8 +482,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B58" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B58" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B77" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B77" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Tag"/>
@@ -693,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -939,146 +1035,146 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -1086,78 +1182,230 @@
         <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>105</v>
+      </c>
+      <c r="B64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>108</v>
+      </c>
+      <c r="B67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>110</v>
+      </c>
+      <c r="B68" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>75</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B77" t="s">
         <v>33</v>
       </c>
     </row>
